--- a/tests/agent_contract/data/S3_count_rows.xlsx
+++ b/tests/agent_contract/data/S3_count_rows.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -49,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,33 +413,45 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C322"/>
+  <dimension ref="A1:C321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n"/>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>订单号</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>城市</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>订单号</t>
+          <t>ORD1000</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>城市</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>410</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ORD1000</t>
+          <t>ORD1001</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -452,13 +460,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4860</v>
+        <v>4810</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ORD1001</t>
+          <t>ORD1002</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -467,13 +475,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1349</v>
+        <v>278</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ORD1002</t>
+          <t>ORD1003</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -482,13 +490,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4009</v>
+        <v>4553</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ORD1003</t>
+          <t>ORD1004</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -497,13 +505,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2080</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ORD1004</t>
+          <t>ORD1005</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -512,13 +520,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4751</v>
+        <v>4683</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ORD1005</t>
+          <t>ORD1006</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -527,13 +535,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2916</v>
+        <v>2303</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ORD1006</t>
+          <t>ORD1007</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -542,13 +550,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1772</v>
+        <v>2455</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ORD1007</t>
+          <t>ORD1008</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -557,13 +565,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3748</v>
+        <v>3732</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ORD1008</t>
+          <t>ORD1009</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -572,13 +580,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4615</v>
+        <v>870</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ORD1009</t>
+          <t>ORD1010</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -587,13 +595,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2452</v>
+        <v>3041</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ORD1010</t>
+          <t>ORD1011</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -602,13 +610,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4015</v>
+        <v>2510</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ORD1011</t>
+          <t>ORD1012</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -617,13 +625,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3495</v>
+        <v>2933</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ORD1012</t>
+          <t>ORD1013</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -632,13 +640,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1555</v>
+        <v>2422</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ORD1013</t>
+          <t>ORD1014</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -647,13 +655,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4394</v>
+        <v>3111</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ORD1014</t>
+          <t>ORD1015</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -662,13 +670,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>580</v>
+        <v>3825</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ORD1015</t>
+          <t>ORD1016</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -677,13 +685,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2197</v>
+        <v>2961</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ORD1016</t>
+          <t>ORD1017</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -692,13 +700,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>305</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ORD1017</t>
+          <t>ORD1018</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -707,13 +715,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4846</v>
+        <v>182</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ORD1018</t>
+          <t>ORD1019</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -722,13 +730,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2267</v>
+        <v>4451</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ORD1019</t>
+          <t>ORD1020</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -737,13 +745,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1480</v>
+        <v>3835</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ORD1020</t>
+          <t>ORD1021</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -752,13 +760,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1946</v>
+        <v>4948</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ORD1021</t>
+          <t>ORD1022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -767,13 +775,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>844</v>
+        <v>558</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ORD1022</t>
+          <t>ORD1023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -782,13 +790,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>318</v>
+        <v>4833</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ORD1023</t>
+          <t>ORD1024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -797,13 +805,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2849</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ORD1024</t>
+          <t>ORD1025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -812,13 +820,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4740</v>
+        <v>3481</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ORD1025</t>
+          <t>ORD1026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -827,13 +835,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3393</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ORD1026</t>
+          <t>ORD1027</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -842,13 +850,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2970</v>
+        <v>4920</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ORD1027</t>
+          <t>ORD1028</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -857,13 +865,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>221</v>
+        <v>3056</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ORD1028</t>
+          <t>ORD1029</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -872,13 +880,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2587</v>
+        <v>137</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ORD1029</t>
+          <t>ORD1030</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -887,13 +895,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>4189</v>
+        <v>2439</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ORD1030</t>
+          <t>ORD1031</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -902,13 +910,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1728</v>
+        <v>3357</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ORD1031</t>
+          <t>ORD1032</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -917,13 +925,13 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>3669</v>
+        <v>3259</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ORD1032</t>
+          <t>ORD1033</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -932,13 +940,13 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>4660</v>
+        <v>4871</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ORD1033</t>
+          <t>ORD1034</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -947,13 +955,13 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4320</v>
+        <v>4119</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ORD1034</t>
+          <t>ORD1035</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -962,13 +970,13 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2105</v>
+        <v>4824</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ORD1035</t>
+          <t>ORD1036</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -977,13 +985,13 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4578</v>
+        <v>3660</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ORD1036</t>
+          <t>ORD1037</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -992,13 +1000,13 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>773</v>
+        <v>3889</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ORD1037</t>
+          <t>ORD1038</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1007,13 +1015,13 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1867</v>
+        <v>4681</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ORD1038</t>
+          <t>ORD1039</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1022,13 +1030,13 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>719</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ORD1039</t>
+          <t>ORD1040</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1037,13 +1045,13 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1024</v>
+        <v>2057</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ORD1040</t>
+          <t>ORD1041</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1052,13 +1060,13 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1912</v>
+        <v>4706</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ORD1041</t>
+          <t>ORD1042</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1067,13 +1075,13 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2251</v>
+        <v>330</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ORD1042</t>
+          <t>ORD1043</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1082,13 +1090,13 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>4149</v>
+        <v>3032</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ORD1043</t>
+          <t>ORD1044</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1097,13 +1105,13 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>3731</v>
+        <v>2101</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ORD1044</t>
+          <t>ORD1045</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1112,13 +1120,13 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1384</v>
+        <v>4304</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ORD1045</t>
+          <t>ORD1046</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1127,13 +1135,13 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>3333</v>
+        <v>3685</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ORD1046</t>
+          <t>ORD1047</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1142,13 +1150,13 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>4408</v>
+        <v>693</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ORD1047</t>
+          <t>ORD1048</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1157,13 +1165,13 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>716</v>
+        <v>649</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ORD1048</t>
+          <t>ORD1049</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1172,13 +1180,13 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>156</v>
+        <v>3466</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ORD1049</t>
+          <t>ORD1050</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1187,13 +1195,13 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>4427</v>
+        <v>3502</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ORD1050</t>
+          <t>ORD1051</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1202,13 +1210,13 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>4589</v>
+        <v>4319</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ORD1051</t>
+          <t>ORD1052</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1217,13 +1225,13 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>804</v>
+        <v>2626</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ORD1052</t>
+          <t>ORD1053</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1232,13 +1240,13 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>225</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ORD1053</t>
+          <t>ORD1054</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1247,13 +1255,13 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>2912</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ORD1054</t>
+          <t>ORD1055</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1262,13 +1270,13 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1201</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ORD1055</t>
+          <t>ORD1056</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1277,13 +1285,13 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>4977</v>
+        <v>2813</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ORD1056</t>
+          <t>ORD1057</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1292,13 +1300,13 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>2230</v>
+        <v>3149</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ORD1057</t>
+          <t>ORD1058</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1307,13 +1315,13 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1094</v>
+        <v>4413</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ORD1058</t>
+          <t>ORD1059</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1322,13 +1330,13 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>824</v>
+        <v>4660</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ORD1059</t>
+          <t>ORD1060</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1337,13 +1345,13 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>489</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ORD1060</t>
+          <t>ORD1061</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1352,13 +1360,13 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>2111</v>
+        <v>3563</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ORD1061</t>
+          <t>ORD1062</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1367,13 +1375,13 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>804</v>
+        <v>3730</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ORD1062</t>
+          <t>ORD1063</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1382,13 +1390,13 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>4380</v>
+        <v>3137</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ORD1063</t>
+          <t>ORD1064</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1397,13 +1405,13 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>754</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ORD1064</t>
+          <t>ORD1065</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1412,13 +1420,13 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>862</v>
+        <v>3255</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ORD1065</t>
+          <t>ORD1066</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1427,13 +1435,13 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>2642</v>
+        <v>3043</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ORD1066</t>
+          <t>ORD1067</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1442,13 +1450,13 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1627</v>
+        <v>4726</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ORD1067</t>
+          <t>ORD1068</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1457,13 +1465,13 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>744</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ORD1068</t>
+          <t>ORD1069</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1472,13 +1480,13 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>3116</v>
+        <v>2842</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ORD1069</t>
+          <t>ORD1070</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1487,13 +1495,13 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>4394</v>
+        <v>4931</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ORD1070</t>
+          <t>ORD1071</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1502,13 +1510,13 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>2807</v>
+        <v>4663</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ORD1071</t>
+          <t>ORD1072</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -1517,13 +1525,13 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>259</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ORD1072</t>
+          <t>ORD1073</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -1532,13 +1540,13 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>4416</v>
+        <v>2696</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ORD1073</t>
+          <t>ORD1074</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -1547,13 +1555,13 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>3770</v>
+        <v>4953</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ORD1074</t>
+          <t>ORD1075</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -1562,13 +1570,13 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>769</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ORD1075</t>
+          <t>ORD1076</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -1577,13 +1585,13 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>3043</v>
+        <v>4190</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ORD1076</t>
+          <t>ORD1077</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -1592,13 +1600,13 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>4597</v>
+        <v>4825</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ORD1077</t>
+          <t>ORD1078</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -1607,13 +1615,13 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>182</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ORD1078</t>
+          <t>ORD1079</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -1622,13 +1630,13 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1568</v>
+        <v>2315</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ORD1079</t>
+          <t>ORD1080</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -1637,13 +1645,13 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>2425</v>
+        <v>977</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ORD1080</t>
+          <t>ORD1081</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -1652,13 +1660,13 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>193</v>
+        <v>2803</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ORD1081</t>
+          <t>ORD1082</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -1667,13 +1675,13 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1265</v>
+        <v>3496</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ORD1082</t>
+          <t>ORD1083</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -1682,13 +1690,13 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>749</v>
+        <v>3525</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ORD1083</t>
+          <t>ORD1084</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -1697,28 +1705,28 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>3084</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ORD1084</t>
+          <t>ORD1085</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>4405</v>
+        <v>4073</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ORD1085</t>
+          <t>ORD1086</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -1727,13 +1735,13 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>3076</v>
+        <v>3355</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ORD1086</t>
+          <t>ORD1087</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -1742,13 +1750,13 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>1501</v>
+        <v>630</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ORD1087</t>
+          <t>ORD1088</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -1757,13 +1765,13 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>3343</v>
+        <v>4883</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ORD1088</t>
+          <t>ORD1089</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -1772,13 +1780,13 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>261</v>
+        <v>336</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ORD1089</t>
+          <t>ORD1090</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -1787,13 +1795,13 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>698</v>
+        <v>985</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ORD1090</t>
+          <t>ORD1091</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -1802,13 +1810,13 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>191</v>
+        <v>133</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ORD1091</t>
+          <t>ORD1092</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -1817,13 +1825,13 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>3437</v>
+        <v>2419</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ORD1092</t>
+          <t>ORD1093</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -1832,13 +1840,13 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>4658</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ORD1093</t>
+          <t>ORD1094</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -1847,13 +1855,13 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1446</v>
+        <v>403</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ORD1094</t>
+          <t>ORD1095</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -1862,13 +1870,13 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>520</v>
+        <v>569</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ORD1095</t>
+          <t>ORD1096</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -1877,13 +1885,13 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>4157</v>
+        <v>207</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ORD1096</t>
+          <t>ORD1097</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -1892,13 +1900,13 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>4981</v>
+        <v>3639</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ORD1097</t>
+          <t>ORD1098</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -1907,13 +1915,13 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>3807</v>
+        <v>4930</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ORD1098</t>
+          <t>ORD1099</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -1922,13 +1930,13 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>110</v>
+        <v>3023</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ORD1099</t>
+          <t>ORD1100</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -1937,13 +1945,13 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>3648</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ORD1100</t>
+          <t>ORD1101</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -1952,13 +1960,13 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>2431</v>
+        <v>2782</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ORD1101</t>
+          <t>ORD1102</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -1967,13 +1975,13 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>4143</v>
+        <v>4261</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>ORD1102</t>
+          <t>ORD1103</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -1982,13 +1990,13 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>722</v>
+        <v>236</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ORD1103</t>
+          <t>ORD1104</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -1997,13 +2005,13 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>4063</v>
+        <v>492</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ORD1104</t>
+          <t>ORD1105</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -2012,13 +2020,13 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>3344</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ORD1105</t>
+          <t>ORD1106</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -2027,13 +2035,13 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>1936</v>
+        <v>603</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ORD1106</t>
+          <t>ORD1107</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -2042,13 +2050,13 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>3084</v>
+        <v>959</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ORD1107</t>
+          <t>ORD1108</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -2057,13 +2065,13 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>2790</v>
+        <v>658</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ORD1108</t>
+          <t>ORD1109</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -2072,13 +2080,13 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>4844</v>
+        <v>2706</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ORD1109</t>
+          <t>ORD1110</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -2087,13 +2095,13 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>2426</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ORD1110</t>
+          <t>ORD1111</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -2102,13 +2110,13 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>2756</v>
+        <v>2062</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ORD1111</t>
+          <t>ORD1112</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -2117,13 +2125,13 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>4515</v>
+        <v>248</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ORD1112</t>
+          <t>ORD1113</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -2132,13 +2140,13 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>2355</v>
+        <v>3509</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ORD1113</t>
+          <t>ORD1114</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -2147,13 +2155,13 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>2426</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ORD1114</t>
+          <t>ORD1115</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -2162,13 +2170,13 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>2450</v>
+        <v>3542</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ORD1115</t>
+          <t>ORD1116</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -2177,13 +2185,13 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>3560</v>
+        <v>169</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ORD1116</t>
+          <t>ORD1117</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -2192,13 +2200,13 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>2664</v>
+        <v>601</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ORD1117</t>
+          <t>ORD1118</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -2207,13 +2215,13 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>3949</v>
+        <v>3244</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ORD1118</t>
+          <t>ORD1119</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -2222,13 +2230,13 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>2652</v>
+        <v>3400</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ORD1119</t>
+          <t>ORD1120</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -2237,13 +2245,13 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>1552</v>
+        <v>4153</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ORD1120</t>
+          <t>ORD1121</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -2252,13 +2260,13 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>1977</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ORD1121</t>
+          <t>ORD1122</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -2267,13 +2275,13 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>1578</v>
+        <v>4924</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ORD1122</t>
+          <t>ORD1123</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -2282,13 +2290,13 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>2198</v>
+        <v>339</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ORD1123</t>
+          <t>ORD1124</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -2297,13 +2305,13 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>4173</v>
+        <v>4397</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ORD1124</t>
+          <t>ORD1125</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -2312,13 +2320,13 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>1902</v>
+        <v>4982</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ORD1125</t>
+          <t>ORD1126</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -2327,13 +2335,13 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>2167</v>
+        <v>4342</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ORD1126</t>
+          <t>ORD1127</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -2342,13 +2350,13 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>1810</v>
+        <v>3862</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>ORD1127</t>
+          <t>ORD1128</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -2357,13 +2365,13 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>4702</v>
+        <v>829</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ORD1128</t>
+          <t>ORD1129</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -2372,13 +2380,13 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>4691</v>
+        <v>482</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ORD1129</t>
+          <t>ORD1130</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -2387,13 +2395,13 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>4626</v>
+        <v>4549</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ORD1130</t>
+          <t>ORD1131</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -2402,13 +2410,13 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>735</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ORD1131</t>
+          <t>ORD1132</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -2417,13 +2425,13 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>1381</v>
+        <v>4161</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ORD1132</t>
+          <t>ORD1133</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -2432,13 +2440,13 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>1235</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ORD1133</t>
+          <t>ORD1134</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -2447,13 +2455,13 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>2772</v>
+        <v>4547</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ORD1134</t>
+          <t>ORD1135</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -2462,13 +2470,13 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>2542</v>
+        <v>2383</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ORD1135</t>
+          <t>ORD1136</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -2477,13 +2485,13 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>1066</v>
+        <v>214</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ORD1136</t>
+          <t>ORD1137</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -2492,13 +2500,13 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>2753</v>
+        <v>243</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ORD1137</t>
+          <t>ORD1138</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -2507,13 +2515,13 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>1020</v>
+        <v>4464</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ORD1138</t>
+          <t>ORD1139</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -2522,13 +2530,13 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>735</v>
+        <v>263</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ORD1139</t>
+          <t>ORD1140</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -2543,7 +2551,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ORD1140</t>
+          <t>ORD1141</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -2552,13 +2560,13 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>4249</v>
+        <v>3033</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ORD1141</t>
+          <t>ORD1142</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -2567,13 +2575,13 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>2890</v>
+        <v>3397</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ORD1142</t>
+          <t>ORD1143</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -2582,13 +2590,13 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>1128</v>
+        <v>4758</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ORD1143</t>
+          <t>ORD1144</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -2597,13 +2605,13 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>4830</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ORD1144</t>
+          <t>ORD1145</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -2612,13 +2620,13 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>4367</v>
+        <v>3812</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ORD1145</t>
+          <t>ORD1146</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -2627,13 +2635,13 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>4103</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ORD1146</t>
+          <t>ORD1147</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -2642,13 +2650,13 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>2716</v>
+        <v>4854</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ORD1147</t>
+          <t>ORD1148</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -2657,13 +2665,13 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>1477</v>
+        <v>199</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ORD1148</t>
+          <t>ORD1149</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -2672,13 +2680,13 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>4843</v>
+        <v>3745</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ORD1149</t>
+          <t>ORD1150</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -2687,13 +2695,13 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>2484</v>
+        <v>750</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>ORD1150</t>
+          <t>ORD1151</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -2702,13 +2710,13 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>4627</v>
+        <v>3301</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>ORD1151</t>
+          <t>ORD1152</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -2717,13 +2725,13 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>2785</v>
+        <v>3434</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ORD1152</t>
+          <t>ORD1153</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -2732,13 +2740,13 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>1784</v>
+        <v>3596</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ORD1153</t>
+          <t>ORD1154</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -2747,13 +2755,13 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>246</v>
+        <v>3075</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ORD1154</t>
+          <t>ORD1155</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -2762,13 +2770,13 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>452</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>ORD1155</t>
+          <t>ORD1156</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -2777,28 +2785,28 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>3085</v>
+        <v>4291</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ORD1156</t>
+          <t>ORD1157</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>1354</v>
+        <v>3229</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ORD1157</t>
+          <t>ORD1158</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -2807,13 +2815,13 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>2621</v>
+        <v>4192</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ORD1158</t>
+          <t>ORD1159</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -2822,13 +2830,13 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>1042</v>
+        <v>4088</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ORD1159</t>
+          <t>ORD1160</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -2837,13 +2845,13 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>4419</v>
+        <v>4773</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ORD1160</t>
+          <t>ORD1161</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -2852,13 +2860,13 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>900</v>
+        <v>3386</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ORD1161</t>
+          <t>ORD1162</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -2867,13 +2875,13 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>1205</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ORD1162</t>
+          <t>ORD1163</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -2882,13 +2890,13 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>656</v>
+        <v>222</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ORD1163</t>
+          <t>ORD1164</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -2897,13 +2905,13 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>3080</v>
+        <v>2057</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>ORD1164</t>
+          <t>ORD1165</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -2912,13 +2920,13 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>4608</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>ORD1165</t>
+          <t>ORD1166</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -2927,13 +2935,13 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>3500</v>
+        <v>3774</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>ORD1166</t>
+          <t>ORD1167</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -2942,13 +2950,13 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>4734</v>
+        <v>3291</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>ORD1167</t>
+          <t>ORD1168</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -2957,13 +2965,13 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>2702</v>
+        <v>277</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>ORD1168</t>
+          <t>ORD1169</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -2972,13 +2980,13 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>128</v>
+        <v>108</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>ORD1169</t>
+          <t>ORD1170</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -2987,13 +2995,13 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>654</v>
+        <v>2652</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>ORD1170</t>
+          <t>ORD1171</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -3002,13 +3010,13 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>4073</v>
+        <v>3122</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>ORD1171</t>
+          <t>ORD1172</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -3017,13 +3025,13 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>513</v>
+        <v>266</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>ORD1172</t>
+          <t>ORD1173</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -3032,13 +3040,13 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>1075</v>
+        <v>3802</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>ORD1173</t>
+          <t>ORD1174</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -3047,13 +3055,13 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>2536</v>
+        <v>636</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>ORD1174</t>
+          <t>ORD1175</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -3062,13 +3070,13 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>4403</v>
+        <v>4484</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>ORD1175</t>
+          <t>ORD1176</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -3077,13 +3085,13 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>4270</v>
+        <v>488</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>ORD1176</t>
+          <t>ORD1177</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -3092,13 +3100,13 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>1211</v>
+        <v>4602</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>ORD1177</t>
+          <t>ORD1178</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -3107,13 +3115,13 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>4036</v>
+        <v>934</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>ORD1178</t>
+          <t>ORD1179</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -3122,13 +3130,13 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>3246</v>
+        <v>3474</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>ORD1179</t>
+          <t>ORD1180</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -3137,13 +3145,13 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>758</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>ORD1180</t>
+          <t>ORD1181</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -3152,13 +3160,13 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>1603</v>
+        <v>2828</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>ORD1181</t>
+          <t>ORD1182</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -3167,13 +3175,13 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>541</v>
+        <v>2712</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>ORD1182</t>
+          <t>ORD1183</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -3182,13 +3190,13 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>111</v>
+        <v>4175</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>ORD1183</t>
+          <t>ORD1184</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -3197,13 +3205,13 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>3831</v>
+        <v>3435</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>ORD1184</t>
+          <t>ORD1185</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -3212,13 +3220,13 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>2434</v>
+        <v>3514</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>ORD1185</t>
+          <t>ORD1186</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -3227,13 +3235,13 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>4308</v>
+        <v>4812</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>ORD1186</t>
+          <t>ORD1187</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -3242,13 +3250,13 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>4810</v>
+        <v>4061</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>ORD1187</t>
+          <t>ORD1188</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -3257,13 +3265,13 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>4199</v>
+        <v>684</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>ORD1188</t>
+          <t>ORD1189</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -3272,13 +3280,13 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>2716</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>ORD1189</t>
+          <t>ORD1190</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -3287,13 +3295,13 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>3015</v>
+        <v>3663</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>ORD1190</t>
+          <t>ORD1191</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -3302,13 +3310,13 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>772</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>ORD1191</t>
+          <t>ORD1192</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -3317,13 +3325,13 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>4446</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>ORD1192</t>
+          <t>ORD1193</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -3332,13 +3340,13 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>2921</v>
+        <v>3818</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>ORD1193</t>
+          <t>ORD1194</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -3347,13 +3355,13 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>3764</v>
+        <v>161</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>ORD1194</t>
+          <t>ORD1195</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -3362,13 +3370,13 @@
         </is>
       </c>
       <c r="C197" t="n">
-        <v>915</v>
+        <v>3153</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>ORD1195</t>
+          <t>ORD1196</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -3377,13 +3385,13 @@
         </is>
       </c>
       <c r="C198" t="n">
-        <v>1158</v>
+        <v>3988</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>ORD1196</t>
+          <t>ORD1197</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -3392,13 +3400,13 @@
         </is>
       </c>
       <c r="C199" t="n">
-        <v>1542</v>
+        <v>2374</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>ORD1197</t>
+          <t>ORD1198</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -3407,13 +3415,13 @@
         </is>
       </c>
       <c r="C200" t="n">
-        <v>3200</v>
+        <v>4286</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>ORD1198</t>
+          <t>ORD1199</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -3422,13 +3430,13 @@
         </is>
       </c>
       <c r="C201" t="n">
-        <v>4963</v>
+        <v>526</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>ORD1199</t>
+          <t>ORD1200</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -3437,13 +3445,13 @@
         </is>
       </c>
       <c r="C202" t="n">
-        <v>4942</v>
+        <v>2619</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>ORD1200</t>
+          <t>ORD1201</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -3452,13 +3460,13 @@
         </is>
       </c>
       <c r="C203" t="n">
-        <v>2067</v>
+        <v>3888</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>ORD1201</t>
+          <t>ORD1202</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -3467,13 +3475,13 @@
         </is>
       </c>
       <c r="C204" t="n">
-        <v>4766</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>ORD1202</t>
+          <t>ORD1203</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -3482,13 +3490,13 @@
         </is>
       </c>
       <c r="C205" t="n">
-        <v>1699</v>
+        <v>2233</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>ORD1203</t>
+          <t>ORD1204</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -3497,13 +3505,13 @@
         </is>
       </c>
       <c r="C206" t="n">
-        <v>2894</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>ORD1204</t>
+          <t>ORD1205</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -3512,13 +3520,13 @@
         </is>
       </c>
       <c r="C207" t="n">
-        <v>1504</v>
+        <v>3082</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>ORD1205</t>
+          <t>ORD1206</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -3527,13 +3535,13 @@
         </is>
       </c>
       <c r="C208" t="n">
-        <v>2294</v>
+        <v>2202</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>ORD1206</t>
+          <t>ORD1207</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -3542,13 +3550,13 @@
         </is>
       </c>
       <c r="C209" t="n">
-        <v>732</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>ORD1207</t>
+          <t>ORD1208</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -3557,13 +3565,13 @@
         </is>
       </c>
       <c r="C210" t="n">
-        <v>4785</v>
+        <v>4165</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>ORD1208</t>
+          <t>ORD1209</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -3572,13 +3580,13 @@
         </is>
       </c>
       <c r="C211" t="n">
-        <v>1866</v>
+        <v>4018</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>ORD1209</t>
+          <t>ORD1210</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -3587,13 +3595,13 @@
         </is>
       </c>
       <c r="C212" t="n">
-        <v>2501</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>ORD1210</t>
+          <t>ORD1211</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -3602,13 +3610,13 @@
         </is>
       </c>
       <c r="C213" t="n">
-        <v>4220</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>ORD1211</t>
+          <t>ORD1212</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -3617,13 +3625,13 @@
         </is>
       </c>
       <c r="C214" t="n">
-        <v>4215</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>ORD1212</t>
+          <t>ORD1213</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -3632,13 +3640,13 @@
         </is>
       </c>
       <c r="C215" t="n">
-        <v>909</v>
+        <v>823</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>ORD1213</t>
+          <t>ORD1214</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -3647,28 +3655,28 @@
         </is>
       </c>
       <c r="C216" t="n">
-        <v>2010</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>ORD1214</t>
+          <t>ORD1215</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>1348</v>
+        <v>4668</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>ORD1215</t>
+          <t>ORD1216</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -3677,13 +3685,13 @@
         </is>
       </c>
       <c r="C218" t="n">
-        <v>453</v>
+        <v>3294</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>ORD1216</t>
+          <t>ORD1217</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -3692,13 +3700,13 @@
         </is>
       </c>
       <c r="C219" t="n">
-        <v>2673</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>ORD1217</t>
+          <t>ORD1218</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -3707,13 +3715,13 @@
         </is>
       </c>
       <c r="C220" t="n">
-        <v>2846</v>
+        <v>3774</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>ORD1218</t>
+          <t>ORD1219</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -3722,13 +3730,13 @@
         </is>
       </c>
       <c r="C221" t="n">
-        <v>435</v>
+        <v>916</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>ORD1219</t>
+          <t>ORD1220</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -3737,13 +3745,13 @@
         </is>
       </c>
       <c r="C222" t="n">
-        <v>3400</v>
+        <v>4722</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>ORD1220</t>
+          <t>ORD1221</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -3752,13 +3760,13 @@
         </is>
       </c>
       <c r="C223" t="n">
-        <v>4159</v>
+        <v>4323</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>ORD1221</t>
+          <t>ORD1222</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -3767,13 +3775,13 @@
         </is>
       </c>
       <c r="C224" t="n">
-        <v>3373</v>
+        <v>4969</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>ORD1222</t>
+          <t>ORD1223</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -3782,13 +3790,13 @@
         </is>
       </c>
       <c r="C225" t="n">
-        <v>492</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>ORD1223</t>
+          <t>ORD1224</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -3797,13 +3805,13 @@
         </is>
       </c>
       <c r="C226" t="n">
-        <v>937</v>
+        <v>308</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>ORD1224</t>
+          <t>ORD1225</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -3812,13 +3820,13 @@
         </is>
       </c>
       <c r="C227" t="n">
-        <v>3339</v>
+        <v>2540</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>ORD1225</t>
+          <t>ORD1226</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -3827,13 +3835,13 @@
         </is>
       </c>
       <c r="C228" t="n">
-        <v>4240</v>
+        <v>2746</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>ORD1226</t>
+          <t>ORD1227</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -3842,13 +3850,13 @@
         </is>
       </c>
       <c r="C229" t="n">
-        <v>1611</v>
+        <v>694</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>ORD1227</t>
+          <t>ORD1228</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -3857,13 +3865,13 @@
         </is>
       </c>
       <c r="C230" t="n">
-        <v>4931</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>ORD1228</t>
+          <t>ORD1229</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -3872,13 +3880,13 @@
         </is>
       </c>
       <c r="C231" t="n">
-        <v>532</v>
+        <v>3781</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>ORD1229</t>
+          <t>ORD1230</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -3887,13 +3895,13 @@
         </is>
       </c>
       <c r="C232" t="n">
-        <v>1537</v>
+        <v>4104</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>ORD1230</t>
+          <t>ORD1231</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -3902,13 +3910,13 @@
         </is>
       </c>
       <c r="C233" t="n">
-        <v>676</v>
+        <v>3440</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>ORD1231</t>
+          <t>ORD1232</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -3917,13 +3925,13 @@
         </is>
       </c>
       <c r="C234" t="n">
-        <v>3668</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>ORD1232</t>
+          <t>ORD1233</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -3932,13 +3940,13 @@
         </is>
       </c>
       <c r="C235" t="n">
-        <v>1323</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>ORD1233</t>
+          <t>ORD1234</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -3947,13 +3955,13 @@
         </is>
       </c>
       <c r="C236" t="n">
-        <v>2987</v>
+        <v>708</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>ORD1234</t>
+          <t>ORD1235</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -3962,13 +3970,13 @@
         </is>
       </c>
       <c r="C237" t="n">
-        <v>1655</v>
+        <v>273</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>ORD1235</t>
+          <t>ORD1236</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -3977,13 +3985,13 @@
         </is>
       </c>
       <c r="C238" t="n">
-        <v>4032</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>ORD1236</t>
+          <t>ORD1237</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -3992,13 +4000,13 @@
         </is>
       </c>
       <c r="C239" t="n">
-        <v>1122</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>ORD1237</t>
+          <t>ORD1238</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -4007,13 +4015,13 @@
         </is>
       </c>
       <c r="C240" t="n">
-        <v>2903</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>ORD1238</t>
+          <t>ORD1239</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -4022,13 +4030,13 @@
         </is>
       </c>
       <c r="C241" t="n">
-        <v>4268</v>
+        <v>4547</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>ORD1239</t>
+          <t>ORD1240</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -4037,13 +4045,13 @@
         </is>
       </c>
       <c r="C242" t="n">
-        <v>2415</v>
+        <v>3743</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>ORD1240</t>
+          <t>ORD1241</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -4052,13 +4060,13 @@
         </is>
       </c>
       <c r="C243" t="n">
-        <v>4742</v>
+        <v>4352</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>ORD1241</t>
+          <t>ORD1242</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -4067,13 +4075,13 @@
         </is>
       </c>
       <c r="C244" t="n">
-        <v>915</v>
+        <v>908</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>ORD1242</t>
+          <t>ORD1243</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -4082,13 +4090,13 @@
         </is>
       </c>
       <c r="C245" t="n">
-        <v>2644</v>
+        <v>4005</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>ORD1243</t>
+          <t>ORD1244</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -4097,13 +4105,13 @@
         </is>
       </c>
       <c r="C246" t="n">
-        <v>628</v>
+        <v>4435</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>ORD1244</t>
+          <t>ORD1245</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -4112,13 +4120,13 @@
         </is>
       </c>
       <c r="C247" t="n">
-        <v>2744</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>ORD1245</t>
+          <t>ORD1246</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -4127,13 +4135,13 @@
         </is>
       </c>
       <c r="C248" t="n">
-        <v>2796</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>ORD1246</t>
+          <t>ORD1247</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -4142,13 +4150,13 @@
         </is>
       </c>
       <c r="C249" t="n">
-        <v>2897</v>
+        <v>2894</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>ORD1247</t>
+          <t>ORD1248</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -4157,13 +4165,13 @@
         </is>
       </c>
       <c r="C250" t="n">
-        <v>3002</v>
+        <v>365</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>ORD1248</t>
+          <t>ORD1249</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -4172,13 +4180,13 @@
         </is>
       </c>
       <c r="C251" t="n">
-        <v>185</v>
+        <v>446</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>ORD1249</t>
+          <t>ORD1250</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -4187,13 +4195,13 @@
         </is>
       </c>
       <c r="C252" t="n">
-        <v>3600</v>
+        <v>2071</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>ORD1250</t>
+          <t>ORD1251</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -4202,13 +4210,13 @@
         </is>
       </c>
       <c r="C253" t="n">
-        <v>261</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>ORD1251</t>
+          <t>ORD1252</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -4217,13 +4225,13 @@
         </is>
       </c>
       <c r="C254" t="n">
-        <v>2423</v>
+        <v>4511</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>ORD1252</t>
+          <t>ORD1253</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -4232,13 +4240,13 @@
         </is>
       </c>
       <c r="C255" t="n">
-        <v>1800</v>
+        <v>4464</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>ORD1253</t>
+          <t>ORD1254</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -4247,13 +4255,13 @@
         </is>
       </c>
       <c r="C256" t="n">
-        <v>4812</v>
+        <v>2911</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>ORD1254</t>
+          <t>ORD1255</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -4262,13 +4270,13 @@
         </is>
       </c>
       <c r="C257" t="n">
-        <v>3076</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>ORD1255</t>
+          <t>ORD1256</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -4277,28 +4285,28 @@
         </is>
       </c>
       <c r="C258" t="n">
-        <v>3574</v>
+        <v>3032</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>ORD1256</t>
+          <t>ORD1257</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="C259" t="n">
-        <v>3398</v>
+        <v>2617</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>ORD1257</t>
+          <t>ORD1258</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -4307,13 +4315,13 @@
         </is>
       </c>
       <c r="C260" t="n">
-        <v>1497</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>ORD1258</t>
+          <t>ORD1259</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -4322,13 +4330,13 @@
         </is>
       </c>
       <c r="C261" t="n">
-        <v>2487</v>
+        <v>3009</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>ORD1259</t>
+          <t>ORD1260</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -4337,13 +4345,13 @@
         </is>
       </c>
       <c r="C262" t="n">
-        <v>3783</v>
+        <v>3238</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>ORD1260</t>
+          <t>ORD1261</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -4352,13 +4360,13 @@
         </is>
       </c>
       <c r="C263" t="n">
-        <v>1048</v>
+        <v>3607</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>ORD1261</t>
+          <t>ORD1262</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -4367,13 +4375,13 @@
         </is>
       </c>
       <c r="C264" t="n">
-        <v>4009</v>
+        <v>289</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>ORD1262</t>
+          <t>ORD1263</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -4382,13 +4390,13 @@
         </is>
       </c>
       <c r="C265" t="n">
-        <v>3487</v>
+        <v>932</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>ORD1263</t>
+          <t>ORD1264</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -4397,13 +4405,13 @@
         </is>
       </c>
       <c r="C266" t="n">
-        <v>2192</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>ORD1264</t>
+          <t>ORD1265</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -4412,13 +4420,13 @@
         </is>
       </c>
       <c r="C267" t="n">
-        <v>2987</v>
+        <v>4482</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>ORD1265</t>
+          <t>ORD1266</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -4427,13 +4435,13 @@
         </is>
       </c>
       <c r="C268" t="n">
-        <v>1373</v>
+        <v>3655</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>ORD1266</t>
+          <t>ORD1267</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -4442,13 +4450,13 @@
         </is>
       </c>
       <c r="C269" t="n">
-        <v>2385</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>ORD1267</t>
+          <t>ORD1268</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -4457,13 +4465,13 @@
         </is>
       </c>
       <c r="C270" t="n">
-        <v>1707</v>
+        <v>4745</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>ORD1268</t>
+          <t>ORD1269</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -4472,13 +4480,13 @@
         </is>
       </c>
       <c r="C271" t="n">
-        <v>115</v>
+        <v>763</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>ORD1269</t>
+          <t>ORD1270</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -4487,13 +4495,13 @@
         </is>
       </c>
       <c r="C272" t="n">
-        <v>3318</v>
+        <v>4827</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>ORD1270</t>
+          <t>ORD1271</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -4502,13 +4510,13 @@
         </is>
       </c>
       <c r="C273" t="n">
-        <v>2612</v>
+        <v>4252</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>ORD1271</t>
+          <t>ORD1272</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -4517,13 +4525,13 @@
         </is>
       </c>
       <c r="C274" t="n">
-        <v>2762</v>
+        <v>4531</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>ORD1272</t>
+          <t>ORD1273</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -4532,13 +4540,13 @@
         </is>
       </c>
       <c r="C275" t="n">
-        <v>567</v>
+        <v>3434</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>ORD1273</t>
+          <t>ORD1274</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -4547,13 +4555,13 @@
         </is>
       </c>
       <c r="C276" t="n">
-        <v>4973</v>
+        <v>328</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>ORD1274</t>
+          <t>ORD1275</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -4562,13 +4570,13 @@
         </is>
       </c>
       <c r="C277" t="n">
-        <v>2234</v>
+        <v>3797</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>ORD1275</t>
+          <t>ORD1276</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -4577,13 +4585,13 @@
         </is>
       </c>
       <c r="C278" t="n">
-        <v>3446</v>
+        <v>4229</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>ORD1276</t>
+          <t>ORD1277</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -4592,13 +4600,13 @@
         </is>
       </c>
       <c r="C279" t="n">
-        <v>1379</v>
+        <v>2747</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>ORD1277</t>
+          <t>ORD1278</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -4607,13 +4615,13 @@
         </is>
       </c>
       <c r="C280" t="n">
-        <v>3889</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>ORD1278</t>
+          <t>ORD1279</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -4622,13 +4630,13 @@
         </is>
       </c>
       <c r="C281" t="n">
-        <v>2957</v>
+        <v>3621</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>ORD1279</t>
+          <t>ORD1280</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -4637,13 +4645,13 @@
         </is>
       </c>
       <c r="C282" t="n">
-        <v>2851</v>
+        <v>2326</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>ORD1280</t>
+          <t>ORD1281</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -4652,13 +4660,13 @@
         </is>
       </c>
       <c r="C283" t="n">
-        <v>1983</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>ORD1281</t>
+          <t>ORD1282</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -4667,13 +4675,13 @@
         </is>
       </c>
       <c r="C284" t="n">
-        <v>3804</v>
+        <v>3868</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>ORD1282</t>
+          <t>ORD1283</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -4682,13 +4690,13 @@
         </is>
       </c>
       <c r="C285" t="n">
-        <v>3408</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>ORD1283</t>
+          <t>ORD1284</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -4697,28 +4705,28 @@
         </is>
       </c>
       <c r="C286" t="n">
-        <v>3244</v>
+        <v>265</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>ORD1284</t>
+          <t>ORD1285</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="C287" t="n">
-        <v>2468</v>
+        <v>2453</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>ORD1285</t>
+          <t>ORD1286</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -4727,13 +4735,13 @@
         </is>
       </c>
       <c r="C288" t="n">
-        <v>4229</v>
+        <v>2676</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>ORD1286</t>
+          <t>ORD1287</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -4742,13 +4750,13 @@
         </is>
       </c>
       <c r="C289" t="n">
-        <v>2725</v>
+        <v>3771</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>ORD1287</t>
+          <t>ORD1288</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -4757,13 +4765,13 @@
         </is>
       </c>
       <c r="C290" t="n">
-        <v>3757</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>ORD1288</t>
+          <t>ORD1289</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -4772,13 +4780,13 @@
         </is>
       </c>
       <c r="C291" t="n">
-        <v>847</v>
+        <v>4375</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>ORD1289</t>
+          <t>ORD1290</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -4787,13 +4795,13 @@
         </is>
       </c>
       <c r="C292" t="n">
-        <v>1099</v>
+        <v>3438</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>ORD1290</t>
+          <t>ORD1291</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -4802,13 +4810,13 @@
         </is>
       </c>
       <c r="C293" t="n">
-        <v>1034</v>
+        <v>3451</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>ORD1291</t>
+          <t>ORD1292</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -4817,13 +4825,13 @@
         </is>
       </c>
       <c r="C294" t="n">
-        <v>3695</v>
+        <v>3229</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>ORD1292</t>
+          <t>ORD1293</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -4832,13 +4840,13 @@
         </is>
       </c>
       <c r="C295" t="n">
-        <v>2281</v>
+        <v>3239</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>ORD1293</t>
+          <t>ORD1294</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -4847,13 +4855,13 @@
         </is>
       </c>
       <c r="C296" t="n">
-        <v>3817</v>
+        <v>4756</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>ORD1294</t>
+          <t>ORD1295</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -4862,13 +4870,13 @@
         </is>
       </c>
       <c r="C297" t="n">
-        <v>3410</v>
+        <v>3389</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>ORD1295</t>
+          <t>ORD1296</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -4877,13 +4885,13 @@
         </is>
       </c>
       <c r="C298" t="n">
-        <v>1084</v>
+        <v>756</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>ORD1296</t>
+          <t>ORD1297</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -4892,13 +4900,13 @@
         </is>
       </c>
       <c r="C299" t="n">
-        <v>3299</v>
+        <v>2596</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>ORD1297</t>
+          <t>ORD1298</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -4907,13 +4915,13 @@
         </is>
       </c>
       <c r="C300" t="n">
-        <v>4219</v>
+        <v>4237</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>ORD1298</t>
+          <t>ORD1299</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -4922,13 +4930,13 @@
         </is>
       </c>
       <c r="C301" t="n">
-        <v>2598</v>
+        <v>3750</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>ORD1299</t>
+          <t>ORD1300</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -4937,13 +4945,13 @@
         </is>
       </c>
       <c r="C302" t="n">
-        <v>2577</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>ORD1300</t>
+          <t>ORD1301</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -4952,13 +4960,13 @@
         </is>
       </c>
       <c r="C303" t="n">
-        <v>2277</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>ORD1301</t>
+          <t>ORD1302</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -4967,28 +4975,28 @@
         </is>
       </c>
       <c r="C304" t="n">
-        <v>4711</v>
+        <v>2975</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>ORD1302</t>
+          <t>ORD1303</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="C305" t="n">
-        <v>4707</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>ORD1303</t>
+          <t>ORD1304</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -4997,13 +5005,13 @@
         </is>
       </c>
       <c r="C306" t="n">
-        <v>2038</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>ORD1304</t>
+          <t>ORD1305</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -5012,13 +5020,13 @@
         </is>
       </c>
       <c r="C307" t="n">
-        <v>4379</v>
+        <v>4837</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>ORD1305</t>
+          <t>ORD1306</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -5027,13 +5035,13 @@
         </is>
       </c>
       <c r="C308" t="n">
-        <v>1194</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>ORD1306</t>
+          <t>ORD1307</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -5042,13 +5050,13 @@
         </is>
       </c>
       <c r="C309" t="n">
-        <v>4147</v>
+        <v>779</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>ORD1307</t>
+          <t>ORD1308</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -5057,13 +5065,13 @@
         </is>
       </c>
       <c r="C310" t="n">
-        <v>3715</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>ORD1308</t>
+          <t>ORD1309</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -5072,13 +5080,13 @@
         </is>
       </c>
       <c r="C311" t="n">
-        <v>962</v>
+        <v>2547</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>ORD1309</t>
+          <t>ORD1310</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -5087,13 +5095,13 @@
         </is>
       </c>
       <c r="C312" t="n">
-        <v>2352</v>
+        <v>773</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>ORD1310</t>
+          <t>ORD1311</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -5102,13 +5110,13 @@
         </is>
       </c>
       <c r="C313" t="n">
-        <v>3978</v>
+        <v>594</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>ORD1311</t>
+          <t>ORD1312</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -5117,13 +5125,13 @@
         </is>
       </c>
       <c r="C314" t="n">
-        <v>4288</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>ORD1312</t>
+          <t>ORD1313</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -5132,13 +5140,13 @@
         </is>
       </c>
       <c r="C315" t="n">
-        <v>2194</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>ORD1313</t>
+          <t>ORD1314</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -5147,28 +5155,28 @@
         </is>
       </c>
       <c r="C316" t="n">
-        <v>2097</v>
+        <v>4850</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>ORD1314</t>
+          <t>ORD1315</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>西安</t>
         </is>
       </c>
       <c r="C317" t="n">
-        <v>2175</v>
+        <v>3608</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>ORD1315</t>
+          <t>ORD1316</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -5177,13 +5185,13 @@
         </is>
       </c>
       <c r="C318" t="n">
-        <v>663</v>
+        <v>3285</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>ORD1316</t>
+          <t>ORD1317</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -5192,13 +5200,13 @@
         </is>
       </c>
       <c r="C319" t="n">
-        <v>2367</v>
+        <v>4153</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>ORD1317</t>
+          <t>ORD1318</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -5207,13 +5215,13 @@
         </is>
       </c>
       <c r="C320" t="n">
-        <v>2689</v>
+        <v>3810</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>ORD1318</t>
+          <t>ORD1319</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -5222,22 +5230,7 @@
         </is>
       </c>
       <c r="C321" t="n">
-        <v>1872</v>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" t="inlineStr">
-        <is>
-          <t>ORD1319</t>
-        </is>
-      </c>
-      <c r="B322" t="inlineStr">
-        <is>
-          <t>西安</t>
-        </is>
-      </c>
-      <c r="C322" t="n">
-        <v>2118</v>
+        <v>2030</v>
       </c>
     </row>
   </sheetData>
